--- a/Documentos/ACT-123 Instructions con celdas.xlsx
+++ b/Documentos/ACT-123 Instructions con celdas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\M2A (GD)\CARRETERAS\DOCUMENTOS CARRETERAS\FORMAS Y DOCUMENTOS ACT\Formas con celdas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8E19B5-29F4-4A29-95D6-C0BFD609661E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870BF66C-0950-4BB1-984C-0CAFE08D1047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25515" yWindow="0" windowWidth="18900" windowHeight="10890" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{CFD7E79D-3C06-4201-894B-47EA50F91F3B}"/>
+    <workbookView xWindow="-25320" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{CFD7E79D-3C06-4201-894B-47EA50F91F3B}"/>
   </bookViews>
   <sheets>
     <sheet name="CHO-ACT-YYY" sheetId="21" state="hidden" r:id="rId1"/>
@@ -1310,32 +1310,6 @@
     <t>Fecha de Vigencia en el Contralor Revisada con este documento (Fecha de terminación revisada más (+) 730 días)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">En proyectos de más antiguedad este número es el de </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Purshase Order (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PO). Para proyectos recientes N/A</t>
-    </r>
-  </si>
-  <si>
     <t>Nombre del Representante del Contratista (nombre con sus 2 apellidos). La persona que firma debe estar autorizada en el RUL. De no ser así, deben presentar la resolución corporativa autorizando a la persona que firmará por parte del contratista.</t>
   </si>
   <si>
@@ -1395,21 +1369,6 @@
     <t>q29</t>
   </si>
   <si>
-    <t>aa24</t>
-  </si>
-  <si>
-    <t>c26</t>
-  </si>
-  <si>
-    <t>p26</t>
-  </si>
-  <si>
-    <t>i28</t>
-  </si>
-  <si>
-    <t>z28</t>
-  </si>
-  <si>
     <t>h33</t>
   </si>
   <si>
@@ -1444,6 +1403,47 @@
   </si>
   <si>
     <t>ae60</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En proyectos de más antiguedad este número es el de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Purshase Order (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PO). Para proyectos recientes poner: N/A</t>
+    </r>
+  </si>
+  <si>
+    <t>c26 y d57</t>
+  </si>
+  <si>
+    <t>i28 y ae56</t>
+  </si>
+  <si>
+    <t>z28 y ae57</t>
+  </si>
+  <si>
+    <t>p26 y ae58</t>
+  </si>
+  <si>
+    <t>aa24 y d56</t>
   </si>
 </sst>
 </file>
@@ -14643,7 +14643,7 @@
       </c>
       <c r="D2" s="178"/>
       <c r="E2" s="169" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="D3" s="178"/>
       <c r="E3" s="169" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="D4" s="178"/>
       <c r="E4" s="169" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -14684,11 +14684,11 @@
         <v>44</v>
       </c>
       <c r="C5" s="177" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="D5" s="178"/>
       <c r="E5" s="169" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="D6" s="178"/>
       <c r="E6" s="169" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -14718,17 +14718,17 @@
       </c>
       <c r="D7" s="178"/>
       <c r="E7" s="169" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="171"/>
       <c r="C8" s="177" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D8" s="178"/>
       <c r="E8" s="169" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="48.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="D9" s="178"/>
       <c r="E9" s="169" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="D10" s="178"/>
       <c r="E10" s="169" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="D11" s="178"/>
       <c r="E11" s="169" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="D12" s="178"/>
       <c r="E12" s="169" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="D16" s="178"/>
       <c r="E16" s="169" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="D17" s="178"/>
       <c r="E17" s="169" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -14856,11 +14856,11 @@
         <v>44</v>
       </c>
       <c r="C18" s="177" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D18" s="178"/>
       <c r="E18" s="169" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="D19" s="178"/>
       <c r="E19" s="169" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="D20" s="178"/>
       <c r="E20" s="169" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="D21" s="178"/>
       <c r="E21" s="169" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="D22" s="178"/>
       <c r="E22" s="169" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="D23" s="178"/>
       <c r="E23" s="169" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="D24" s="178"/>
       <c r="E24" s="169" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="D25" s="178"/>
       <c r="E25" s="169" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="D26" s="178"/>
       <c r="E26" s="169" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="D27" s="178"/>
       <c r="E27" s="169" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="D28" s="178"/>
       <c r="E28" s="169" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="D29" s="178"/>
       <c r="E29" s="169" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="D30" s="178"/>
       <c r="E30" s="169" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="D31" s="178"/>
       <c r="E31" s="169" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
